--- a/data/trending_integrated_20260914_10.xlsx
+++ b/data/trending_integrated_20260914_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6780</v>
+        <v>6775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.05%</t>
+          <t>+22.96%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H2" t="n">
         <v>1.67</v>
@@ -610,7 +610,7 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>39639186525</v>
+        <v>41153695850</v>
       </c>
       <c r="P2" t="n">
         <v>10360</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 보안 대장주로서의 위치 강조와 씨이랩, 엔비디아 관련 뉴스 언급. 주가 상승에 대한 기대감과 일부 하락 우려.</t>
+          <t>AI 보안 및 딥페이크 분야 대장주로서의 재부각 기대. 씨이랩, 엔비디아 CEO 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI 보안', '대장주', '엔비디아']</t>
+          <t>['AI보안', '딥페이크', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17240</v>
+        <v>2880</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+7.35%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.31</v>
+        <v>-2.39</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16060</v>
+        <v>2620</v>
       </c>
       <c r="K3" t="n">
-        <v>16780</v>
+        <v>2745</v>
       </c>
       <c r="L3" t="n">
-        <v>18610</v>
+        <v>3145</v>
       </c>
       <c r="M3" t="n">
-        <v>16230</v>
+        <v>2700</v>
       </c>
       <c r="N3" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="O3" t="n">
-        <v>213789810110</v>
+        <v>79836012426</v>
       </c>
       <c r="P3" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q3" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R3" t="n">
-        <v>-135000</v>
+        <v>-309000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 대한 상반된 전망. 주가 상승에 대한 기대감과 매물대 정리 언급.</t>
+          <t>양자보안 분야 대장주로서의 기대감. 전고점 돌파 및 투기적 거래 경고.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['AI', '양자 보안', '매물대']</t>
+          <t>['양자보안', '대장주', '투경']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14930</v>
+        <v>17130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+2.19%</t>
+          <t>+6.66%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.97</v>
+        <v>0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>396</v>
+        <v>107</v>
       </c>
       <c r="H4" t="n">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14610</v>
+        <v>16060</v>
       </c>
       <c r="K4" t="n">
-        <v>15420</v>
+        <v>16780</v>
       </c>
       <c r="L4" t="n">
-        <v>16510</v>
+        <v>18610</v>
       </c>
       <c r="M4" t="n">
-        <v>14720</v>
+        <v>16230</v>
       </c>
       <c r="N4" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="O4" t="n">
-        <v>81301867985</v>
+        <v>224368807860</v>
       </c>
       <c r="P4" t="n">
-        <v>36200</v>
+        <v>30550</v>
       </c>
       <c r="Q4" t="n">
-        <v>8920</v>
+        <v>6100</v>
       </c>
       <c r="R4" t="n">
-        <v>-23000</v>
+        <v>-135000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>이란-걸프국가 호르무즈 해협 회담 연기 및 국제유가 폭등 관련 주가 상승 기대감. 휴전, 협상 뉴스 시 하한가 우려.</t>
+          <t>AI 보안 관련주로서의 상승 기대감. 2연상 및 대장주로서의 지위 언급. 단기 급등 후 차익 실현에 대한 경계.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈 해협', '회담 연기']</t>
+          <t>['AI보안', '대장주', '양자보안']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14250</v>
+        <v>14890</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.62</v>
+        <v>-1.97</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>235</v>
+        <v>445</v>
       </c>
       <c r="H5" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14150</v>
+        <v>14610</v>
       </c>
       <c r="K5" t="n">
-        <v>13850</v>
+        <v>15420</v>
       </c>
       <c r="L5" t="n">
-        <v>14530</v>
+        <v>16510</v>
       </c>
       <c r="M5" t="n">
-        <v>13800</v>
+        <v>14720</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="O5" t="n">
-        <v>53930617450</v>
+        <v>84260276005</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>36200</v>
       </c>
       <c r="Q5" t="n">
-        <v>1272</v>
+        <v>8920</v>
       </c>
       <c r="R5" t="n">
-        <v>-356000</v>
+        <v>-23000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AIDC 광통신 기술 및 GPU 확보 관련 긍정적 전망. AI 속도 조절론 언급 및 주가 상승 기대.</t>
+          <t>국제 유가 급등 및 호르무즈 해협 회담 연기 소식에도 불구하고 외인, 기관, 프로그램 매도세 출현. WTI 104달러 돌파 직전 상황.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['광통신', 'AIDC', 'GPU']</t>
+          <t>['국제유가', '호르무즈해협', '회담연기']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8280</v>
+        <v>14230</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>481</v>
+        <v>260</v>
       </c>
       <c r="H6" t="n">
-        <v>0.75</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8290</v>
+        <v>14150</v>
       </c>
       <c r="K6" t="n">
-        <v>8100</v>
+        <v>13850</v>
       </c>
       <c r="L6" t="n">
-        <v>9050</v>
+        <v>14530</v>
       </c>
       <c r="M6" t="n">
-        <v>8060</v>
+        <v>13800</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>16679012975</v>
+        <v>56355374905</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>77000</v>
+        <v>-356000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>항암 신약 임상 결과에 대한 긍정적 기대감과 목표 주가 상향. 투자 주의 해제 및 재료 노출 관련 언급.</t>
+          <t>GPU 확보 후 '연결' 중요성 부각되는 가운데 AIDC 광통신 기술 성장 기대. 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['항암 신약', '임상 결과', '목표 주가']</t>
+          <t>['AIDC', '광통신', 'GPU']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88400</v>
+        <v>8280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.03</v>
+        <v>-0.54</v>
       </c>
       <c r="E7" t="n">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>471</v>
+        <v>559</v>
       </c>
       <c r="H7" t="n">
-        <v>23.56</v>
+        <v>0.75</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>90800</v>
+        <v>8290</v>
       </c>
       <c r="K7" t="n">
-        <v>89800</v>
+        <v>8100</v>
       </c>
       <c r="L7" t="n">
-        <v>90400</v>
+        <v>9050</v>
       </c>
       <c r="M7" t="n">
-        <v>87800</v>
+        <v>8060</v>
       </c>
       <c r="N7" t="n">
-        <v>23.59</v>
+        <v>1.29</v>
       </c>
       <c r="O7" t="n">
-        <v>87609090750</v>
+        <v>17218540670</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>-320000</v>
+        <v>77000</v>
       </c>
       <c r="S7" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 가능성 언급. 기관 매집 및 공매도 세력과의 공방 기대.</t>
+          <t>페니트리움바이오, '가짜내성' 타깃 항암 전략 제시하며 글로벌 심포지엄 개최. 임상 결과 및 파텔 교수 발표에 대한 기대감 높음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['국제유가', '원전주', '기관']</t>
+          <t>['항암', '신약', '심포지엄']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>251000</v>
+        <v>1857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.36</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>502</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>1844</v>
+        <v>164</v>
       </c>
       <c r="H8" t="n">
-        <v>46.64</v>
+        <v>2.08</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>259500</v>
+        <v>1878</v>
       </c>
       <c r="K8" t="n">
-        <v>249500</v>
+        <v>1909</v>
       </c>
       <c r="L8" t="n">
-        <v>252500</v>
+        <v>1961</v>
       </c>
       <c r="M8" t="n">
-        <v>249000</v>
+        <v>1855</v>
       </c>
       <c r="N8" t="n">
-        <v>46.71</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1006280887250</v>
+        <v>12388038945</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>4795</v>
       </c>
       <c r="Q8" t="n">
-        <v>75900</v>
+        <v>1524</v>
       </c>
       <c r="R8" t="n">
-        <v>-1189000</v>
+        <v>-192000</v>
       </c>
       <c r="S8" t="n">
-        <v>-852000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 이슈와 반도체 산업 전망에 대한 혼란스러운 논의. 특정 정치인에 대한 비판과 시장 하락 우려가 혼재.</t>
+          <t>홍해 및 호르무즈 해협 불안으로 인한 유조선 운임 상승 전망. 전쟁 테마 관련 언급. 유가 상승으로 인한 원가 상승 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반도체', '정책', '하락']</t>
+          <t>['운임', '유가', '전쟁 테마']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,14 +1200,14 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1215,62 +1215,62 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.78%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.51</v>
+        <v>-0.72</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>17.58</v>
+        <v>0.22</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12450</v>
+        <v>12290</v>
       </c>
       <c r="K9" t="n">
-        <v>11960</v>
+        <v>12030</v>
       </c>
       <c r="L9" t="n">
-        <v>13900</v>
+        <v>13230</v>
       </c>
       <c r="M9" t="n">
-        <v>11810</v>
+        <v>11900</v>
       </c>
       <c r="N9" t="n">
-        <v>17.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>47075644170</v>
+        <v>48545632580</v>
       </c>
       <c r="P9" t="n">
-        <v>14350</v>
+        <v>20850</v>
       </c>
       <c r="Q9" t="n">
-        <v>465</v>
+        <v>4020</v>
       </c>
       <c r="R9" t="n">
-        <v>69000</v>
+        <v>30000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 거래와 외인 수급에 대한 언급. 테마주로서의 가능성과 전환사채 관련 논의.</t>
+          <t>원전주 폭락세 속에서 거래량은 좋으나, 매물대 부담 및 음봉 마감 가능성 제기. 가격 지지선 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['단타', '외인 수급', '전환사채']</t>
+          <t>['원전주', '폭락', '매물대']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18890</v>
+        <v>88000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-5.03%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="G10" t="n">
-        <v>203</v>
+        <v>480</v>
       </c>
       <c r="H10" t="n">
-        <v>10.55</v>
+        <v>23.56</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>19890</v>
+        <v>90800</v>
       </c>
       <c r="K10" t="n">
-        <v>19480</v>
+        <v>89800</v>
       </c>
       <c r="L10" t="n">
-        <v>19550</v>
+        <v>90400</v>
       </c>
       <c r="M10" t="n">
-        <v>18780</v>
+        <v>87800</v>
       </c>
       <c r="N10" t="n">
-        <v>10.65</v>
+        <v>23.59</v>
       </c>
       <c r="O10" t="n">
-        <v>33331192215</v>
+        <v>103424081850</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-224000</v>
+        <v>-320000</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>-89000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>대차해지 운동 독려와 저점 상승 및 위기 기회론 제기. 주가 하락에 대한 불안감도 공존.</t>
+          <t>국제 유가 상승과 연계한 원전주 상승 가능성 언급. 기관 매수세 및 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['대차해지', '저점 상승', '기회']</t>
+          <t>['원전주', '유가', '기관매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13920</v>
+        <v>250000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-5.37%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>509</v>
       </c>
       <c r="G11" t="n">
-        <v>95</v>
+        <v>1745</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>46.64</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14710</v>
+        <v>259500</v>
       </c>
       <c r="K11" t="n">
-        <v>14710</v>
+        <v>249500</v>
       </c>
       <c r="L11" t="n">
-        <v>15420</v>
+        <v>252500</v>
       </c>
       <c r="M11" t="n">
-        <v>13870</v>
+        <v>249000</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="O11" t="n">
-        <v>19697527155</v>
+        <v>1202696640250</v>
       </c>
       <c r="P11" t="n">
-        <v>19380</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3200</v>
+        <v>75900</v>
       </c>
       <c r="R11" t="n">
-        <v>-63000</v>
+        <v>-1189000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-852000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 호재와 시장 하락 및 정치적 이슈가 혼재. 향후 주가 방향에 대한 혼란.</t>
+          <t>정치적 이슈와 관련된 부정적인 언급이 지배적. 반도체 산업 전반에 대한 비관론.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['재건축', '시공사 선정', '하락']</t>
+          <t>['정치', '반도체', '정책']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1706500</v>
+        <v>11910</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-4.34%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.08</v>
+        <v>0.51</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>491</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>1304</v>
+        <v>91</v>
       </c>
       <c r="H12" t="n">
-        <v>50.47</v>
+        <v>17.58</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,60 +1515,336 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1812000</v>
+        <v>12450</v>
       </c>
       <c r="K12" t="n">
-        <v>1707000</v>
+        <v>11960</v>
       </c>
       <c r="L12" t="n">
-        <v>1729000</v>
+        <v>13900</v>
       </c>
       <c r="M12" t="n">
-        <v>1706000</v>
+        <v>11810</v>
       </c>
       <c r="N12" t="n">
-        <v>50.55</v>
+        <v>17.07</v>
       </c>
       <c r="O12" t="n">
-        <v>2088992548500</v>
+        <v>48223132145</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>14350</v>
       </c>
       <c r="Q12" t="n">
-        <v>325000</v>
+        <v>465</v>
       </c>
       <c r="R12" t="n">
-        <v>-662000</v>
+        <v>69000</v>
       </c>
       <c r="S12" t="n">
-        <v>-142000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 산업 몰락 및 주가 하락에 대한 강한 부정적 전망. 공매도 금지 및 현금 보유 권고.</t>
+          <t>단기 급등락과 투기적 거래에 대한 언급. 전환사채 매각 및 수급 불균형에 대한 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '하락', '공매도']</t>
+          <t>['급등주', '전환사채', '수급']</t>
         </is>
       </c>
       <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18880</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-5.08%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>46</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" t="n">
+        <v>213</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>19890</v>
+      </c>
+      <c r="K13" t="n">
+        <v>19480</v>
+      </c>
+      <c r="L13" t="n">
+        <v>19550</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18780</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>36123014625</v>
+      </c>
+      <c r="P13" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>대차해지 운동을 통한 주가 부양에 대한 강력한 요구. 저점 상승 및 기관 매수세 기대.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['대차해지', '주주운동', '기관매수']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1705000</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-5.91%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>500</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1246</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1812000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1701000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2338833700000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>325000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-662000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-142000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>반도체 산업 몰락 및 주가 폭락에 대한 비관론. 정치적 요인 및 공매도에 대한 불만.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['반도체', '몰락', '공매도']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>70</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13800</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-6.19%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>101</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>14710</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14710</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15420</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13800</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>20695998225</v>
+      </c>
+      <c r="P15" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-63000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>수원 파장1구역 재건축 수주 소식이 있으나, 전반적인 주가 하락 및 '망했다'는 부정적 인식이 강함.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['재건축', '시공사', '주가하락']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>53</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>002990</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260914_10.xlsx
+++ b/data/trending_integrated_20260914_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,21 +567,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6775</v>
+        <v>6790</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.96%</t>
+          <t>+23.23%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
         <v>70</v>
@@ -610,7 +610,7 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>41153695850</v>
+        <v>42259790650</v>
       </c>
       <c r="P2" t="n">
         <v>10360</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 분야 대장주로서의 재부각 기대. 씨이랩, 엔비디아 CEO 언급.</t>
+          <t>AI 보안 및 딥페이크 관련주로 재부각, 씨이랩-엔비디아 연관성 언급. 주가 급등.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2880</v>
+        <v>9160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>+15.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.39</v>
+        <v>-0.28</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>121</v>
+        <v>67</v>
       </c>
       <c r="H3" t="n">
-        <v>1.44</v>
+        <v>17.67</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2620</v>
+        <v>7900</v>
       </c>
       <c r="K3" t="n">
-        <v>2745</v>
+        <v>7790</v>
       </c>
       <c r="L3" t="n">
-        <v>3145</v>
+        <v>9500</v>
       </c>
       <c r="M3" t="n">
-        <v>2700</v>
+        <v>7700</v>
       </c>
       <c r="N3" t="n">
-        <v>3.83</v>
+        <v>17.95</v>
       </c>
       <c r="O3" t="n">
-        <v>79836012426</v>
+        <v>119178950005</v>
       </c>
       <c r="P3" t="n">
-        <v>4810</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>1400</v>
+        <v>1760</v>
       </c>
       <c r="R3" t="n">
-        <v>-309000</v>
+        <v>56000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자보안 분야 대장주로서의 기대감. 전고점 돌파 및 투기적 거래 경고.</t>
+          <t>차세대 광반도체 및 광통신 관련주로 부각되며, SK하이닉스 CPO 관련 기대감. 단기 급등 후 조정세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자보안', '대장주', '투경']</t>
+          <t>['광반도체', '광통신', 'CPO']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17130</v>
+        <v>2900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+6.66%</t>
+          <t>+10.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.31</v>
+        <v>-2.39</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16060</v>
+        <v>2620</v>
       </c>
       <c r="K4" t="n">
-        <v>16780</v>
+        <v>2745</v>
       </c>
       <c r="L4" t="n">
-        <v>18610</v>
+        <v>3145</v>
       </c>
       <c r="M4" t="n">
-        <v>16230</v>
+        <v>2700</v>
       </c>
       <c r="N4" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="O4" t="n">
-        <v>224368807860</v>
+        <v>81611069924</v>
       </c>
       <c r="P4" t="n">
-        <v>30550</v>
+        <v>4810</v>
       </c>
       <c r="Q4" t="n">
-        <v>6100</v>
+        <v>1400</v>
       </c>
       <c r="R4" t="n">
-        <v>-135000</v>
+        <v>-309000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AI 보안 관련주로서의 상승 기대감. 2연상 및 대장주로서의 지위 언급. 단기 급등 후 차익 실현에 대한 경계.</t>
+          <t>양자보안 대장주로 부각되며, 매출액 증가 및 전고점 돌파 기대감. 투자경고 조건 충족 시 매도 고려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['AI보안', '대장주', '양자보안']</t>
+          <t>['양자보안', '매출액', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14890</v>
+        <v>17150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+6.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.97</v>
+        <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="F5" t="n">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>445</v>
+        <v>112</v>
       </c>
       <c r="H5" t="n">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14610</v>
+        <v>16060</v>
       </c>
       <c r="K5" t="n">
-        <v>15420</v>
+        <v>16780</v>
       </c>
       <c r="L5" t="n">
-        <v>16510</v>
+        <v>18610</v>
       </c>
       <c r="M5" t="n">
-        <v>14720</v>
+        <v>16230</v>
       </c>
       <c r="N5" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="O5" t="n">
-        <v>84260276005</v>
+        <v>227747252720</v>
       </c>
       <c r="P5" t="n">
-        <v>36200</v>
+        <v>30550</v>
       </c>
       <c r="Q5" t="n">
-        <v>8920</v>
+        <v>6100</v>
       </c>
       <c r="R5" t="n">
-        <v>-23000</v>
+        <v>-135000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 호르무즈 해협 회담 연기 소식에도 불구하고 외인, 기관, 프로그램 매도세 출현. WTI 104달러 돌파 직전 상황.</t>
+          <t>AI 보안 관련주로 2연상 기록, AI 개발 속도 조절론에도 불구하고 상승세 지속. 양자 보안 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈해협', '회담연기']</t>
+          <t>['AI보안', '양자보안', '2연상']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14230</v>
+        <v>15020</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>+2.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.62</v>
+        <v>-1.97</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>184</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>260</v>
+        <v>483</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14150</v>
+        <v>14610</v>
       </c>
       <c r="K6" t="n">
-        <v>13850</v>
+        <v>15420</v>
       </c>
       <c r="L6" t="n">
-        <v>14530</v>
+        <v>16510</v>
       </c>
       <c r="M6" t="n">
-        <v>13800</v>
+        <v>14720</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="O6" t="n">
-        <v>56355374905</v>
+        <v>86036243540</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>36200</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>8920</v>
       </c>
       <c r="R6" t="n">
-        <v>-356000</v>
+        <v>-23000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>GPU 확보 후 '연결' 중요성 부각되는 가운데 AIDC 광통신 기술 성장 기대. 프로그램 매수세 유입.</t>
+          <t>국제 유가 상승세 속에서 지정학적 리스크 부각. 다만, 외인·기관·프로그램 매도세 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AIDC', '광통신', 'GPU']</t>
+          <t>['국제유가', '호르무즈해협', '지정학적리스크']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8280</v>
+        <v>8340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.54</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="H7" t="n">
         <v>0.75</v>
@@ -1070,7 +1070,7 @@
         <v>1.29</v>
       </c>
       <c r="O7" t="n">
-        <v>17218540670</v>
+        <v>17621079710</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>페니트리움바이오, '가짜내성' 타깃 항암 전략 제시하며 글로벌 심포지엄 개최. 임상 결과 및 파텔 교수 발표에 대한 기대감 높음.</t>
+          <t>항암 신약 개발 기대감 속 임상 결과 주목. 글로벌 심포지엄 개최 및 탑급 교수진 발표 예정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['항암', '신약', '심포지엄']</t>
+          <t>['항암신약', '임상결과', '바이오']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1857</v>
+        <v>14180</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.36</v>
+        <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>164</v>
+        <v>329</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1878</v>
+        <v>14150</v>
       </c>
       <c r="K8" t="n">
-        <v>1909</v>
+        <v>13850</v>
       </c>
       <c r="L8" t="n">
-        <v>1961</v>
+        <v>14530</v>
       </c>
       <c r="M8" t="n">
-        <v>1855</v>
+        <v>13800</v>
       </c>
       <c r="N8" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>12388038945</v>
+        <v>58667840275</v>
       </c>
       <c r="P8" t="n">
-        <v>4795</v>
+        <v>31500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1524</v>
+        <v>1272</v>
       </c>
       <c r="R8" t="n">
-        <v>-192000</v>
+        <v>-356000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>홍해 및 호르무즈 해협 불안으로 인한 유조선 운임 상승 전망. 전쟁 테마 관련 언급. 유가 상승으로 인한 원가 상승 우려.</t>
+          <t>AI 성장 기대감 속 광통신 기술력 주목. 일부 투자자 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['운임', '유가', '전쟁 테마']</t>
+          <t>['AI', '광통신', '기술력']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11980</v>
+        <v>11880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.72</v>
+        <v>0.51</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="H9" t="n">
-        <v>0.22</v>
+        <v>17.58</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12290</v>
+        <v>11950</v>
       </c>
       <c r="K9" t="n">
-        <v>12030</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13230</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>11900</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9399999999999999</v>
+        <v>17.07</v>
       </c>
       <c r="O9" t="n">
-        <v>48545632580</v>
+        <v>48860000000</v>
       </c>
       <c r="P9" t="n">
-        <v>20850</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4020</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>30000</v>
+        <v>69000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>원전주 폭락세 속에서 거래량은 좋으나, 매물대 부담 및 음봉 마감 가능성 제기. 가격 지지선 언급.</t>
+          <t>단기 급등주로 거래량 폭증, 외인 수급 변동성과 함께 투자 주의 의견 제기. 추석 전 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '매물대']</t>
+          <t>['단타', '수급', '전환사채']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88000</v>
+        <v>1859</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.03</v>
+        <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="F10" t="n">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>480</v>
+        <v>166</v>
       </c>
       <c r="H10" t="n">
-        <v>23.56</v>
+        <v>2.08</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,130 +1331,130 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>90800</v>
+        <v>1878</v>
       </c>
       <c r="K10" t="n">
-        <v>89800</v>
+        <v>1909</v>
       </c>
       <c r="L10" t="n">
-        <v>90400</v>
+        <v>1961</v>
       </c>
       <c r="M10" t="n">
-        <v>87800</v>
+        <v>1851</v>
       </c>
       <c r="N10" t="n">
-        <v>23.59</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>103424081850</v>
+        <v>12812992248</v>
       </c>
       <c r="P10" t="n">
-        <v>139200</v>
+        <v>4795</v>
       </c>
       <c r="Q10" t="n">
-        <v>57000</v>
+        <v>1524</v>
       </c>
       <c r="R10" t="n">
-        <v>-320000</v>
+        <v>-192000</v>
       </c>
       <c r="S10" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국제 유가 상승과 연계한 원전주 상승 가능성 언급. 기관 매수세 및 공매도 세력에 대한 언급.</t>
+          <t>홍해 및 호르무즈 해협 불안으로 인한 유조선 운임 상승 전망. 전쟁 테마 관련 언급. 유가 상승으로 인한 원가 상승 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전주', '유가', '기관매수']</t>
+          <t>['운임', '유가', '전쟁 테마']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>250000</v>
+        <v>11950</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.66%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>509</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>1745</v>
+        <v>29</v>
       </c>
       <c r="H11" t="n">
-        <v>46.64</v>
+        <v>0.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>259500</v>
+        <v>12290</v>
       </c>
       <c r="K11" t="n">
-        <v>249500</v>
+        <v>12030</v>
       </c>
       <c r="L11" t="n">
-        <v>252500</v>
+        <v>13230</v>
       </c>
       <c r="M11" t="n">
-        <v>249000</v>
+        <v>11820</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>1202696640250</v>
+        <v>49917472185</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>20850</v>
       </c>
       <c r="Q11" t="n">
-        <v>75900</v>
+        <v>4020</v>
       </c>
       <c r="R11" t="n">
-        <v>-1189000</v>
+        <v>30000</v>
       </c>
       <c r="S11" t="n">
-        <v>-852000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적인 언급이 지배적. 반도체 산업 전반에 대한 비관론.</t>
+          <t>원전주 폭락세 속 개별 이슈 부재. 거래량은 양호하나 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '정책']</t>
+          <t>['원전주', '폭락', '거래량']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11910</v>
+        <v>87900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.34%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.51</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="G12" t="n">
-        <v>91</v>
+        <v>498</v>
       </c>
       <c r="H12" t="n">
-        <v>17.58</v>
+        <v>23.56</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12450</v>
+        <v>90800</v>
       </c>
       <c r="K12" t="n">
-        <v>11960</v>
+        <v>89800</v>
       </c>
       <c r="L12" t="n">
-        <v>13900</v>
+        <v>90400</v>
       </c>
       <c r="M12" t="n">
-        <v>11810</v>
+        <v>87700</v>
       </c>
       <c r="N12" t="n">
-        <v>17.07</v>
+        <v>23.59</v>
       </c>
       <c r="O12" t="n">
-        <v>48223132145</v>
+        <v>111161042700</v>
       </c>
       <c r="P12" t="n">
-        <v>14350</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>465</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>69000</v>
+        <v>-320000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-89000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>단기 급등락과 투기적 거래에 대한 언급. 전환사채 매각 및 수급 불균형에 대한 우려.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 기대감, 기관 매수세 및 공매도와의 공방.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['급등주', '전환사채', '수급']</t>
+          <t>['원전', '국제유가', '기관']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18880</v>
+        <v>249500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.08%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>518</v>
       </c>
       <c r="G13" t="n">
-        <v>213</v>
+        <v>1711</v>
       </c>
       <c r="H13" t="n">
-        <v>10.55</v>
+        <v>46.64</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>19890</v>
+        <v>259500</v>
       </c>
       <c r="K13" t="n">
-        <v>19480</v>
+        <v>249500</v>
       </c>
       <c r="L13" t="n">
-        <v>19550</v>
+        <v>252500</v>
       </c>
       <c r="M13" t="n">
-        <v>18780</v>
+        <v>249000</v>
       </c>
       <c r="N13" t="n">
-        <v>10.65</v>
+        <v>46.71</v>
       </c>
       <c r="O13" t="n">
-        <v>36123014625</v>
+        <v>1344900262250</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>75900</v>
       </c>
       <c r="R13" t="n">
-        <v>-224000</v>
+        <v>-1189000</v>
       </c>
       <c r="S13" t="n">
-        <v>5000</v>
+        <v>-852000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대차해지 운동을 통한 주가 부양에 대한 강력한 요구. 저점 상승 및 기관 매수세 기대.</t>
+          <t>정치적 이슈와 맞물려 부정적인 시장 전망 및 반도체 업황에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대차해지', '주주운동', '기관매수']</t>
+          <t>['정치', '반도체', '시장']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1705000</v>
+        <v>18790</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="G14" t="n">
-        <v>1246</v>
+        <v>218</v>
       </c>
       <c r="H14" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K14" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L14" t="n">
-        <v>1729000</v>
+        <v>19550</v>
       </c>
       <c r="M14" t="n">
-        <v>1701000</v>
+        <v>18780</v>
       </c>
       <c r="N14" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O14" t="n">
-        <v>2338833700000</v>
+        <v>38704292445</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-662000</v>
+        <v>-224000</v>
       </c>
       <c r="S14" t="n">
-        <v>-142000</v>
+        <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 산업 몰락 및 주가 폭락에 대한 비관론. 정치적 요인 및 공매도에 대한 불만.</t>
+          <t>대차해지 운동 관련 논의가 활발하며, 저점 상승 추세 및 미국 증시 동반 상승 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '몰락', '공매도']</t>
+          <t>['대차해지', '주주운동', '저점']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13800</v>
+        <v>1695000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-6.19%</t>
+          <t>-6.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>515</v>
       </c>
       <c r="G15" t="n">
-        <v>101</v>
+        <v>1309</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>50.47</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,58 +1791,150 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>14710</v>
+        <v>1812000</v>
       </c>
       <c r="K15" t="n">
-        <v>14710</v>
+        <v>1707000</v>
       </c>
       <c r="L15" t="n">
-        <v>15420</v>
+        <v>1729000</v>
       </c>
       <c r="M15" t="n">
-        <v>13800</v>
+        <v>1695000</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>50.55</v>
       </c>
       <c r="O15" t="n">
-        <v>20695998225</v>
+        <v>2600572503500</v>
       </c>
       <c r="P15" t="n">
-        <v>19380</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>3200</v>
+        <v>325000</v>
       </c>
       <c r="R15" t="n">
-        <v>-63000</v>
+        <v>-662000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-142000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 수주 소식이 있으나, 전반적인 주가 하락 및 '망했다'는 부정적 인식이 강함.</t>
+          <t>반도체 업황 부진 및 정치적 이슈로 인한 하락세, 현금 보유 및 관망세 짙어짐.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['재건축', '시공사', '주가하락']</t>
+          <t>['반도체', '업황', '하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13730</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-6.66%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>54</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36</v>
+      </c>
+      <c r="G16" t="n">
+        <v>107</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>14710</v>
+      </c>
+      <c r="K16" t="n">
+        <v>14710</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15420</v>
+      </c>
+      <c r="M16" t="n">
+        <v>13710</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>22152811860</v>
+      </c>
+      <c r="P16" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-63000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>수원 파장1구역 재건축 시공사 선정 호재에도 불구하고, 주가 하락세 및 공사비 증가 우려.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['재건축', '시공사', '공사비']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
         <v>53</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>002990</t>
         </is>

--- a/data/trending_integrated_20260914_10.xlsx
+++ b/data/trending_integrated_20260914_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6790</v>
+        <v>6810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.23%</t>
+          <t>+23.59%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H2" t="n">
         <v>1.67</v>
@@ -610,7 +610,7 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>42259790650</v>
+        <v>43210945485</v>
       </c>
       <c r="P2" t="n">
         <v>10360</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 관련주로 재부각, 씨이랩-엔비디아 연관성 언급. 주가 급등.</t>
+          <t>AI 보안 및 딥페이크 대장주로서의 기대감 표출. 투경 및 단일가 예고 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9160</v>
+        <v>9080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.95%</t>
+          <t>+14.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.28</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H3" t="n">
         <v>17.67</v>
@@ -702,7 +702,7 @@
         <v>17.95</v>
       </c>
       <c r="O3" t="n">
-        <v>119178950005</v>
+        <v>126915670200</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련주로 부각되며, SK하이닉스 CPO 관련 기대감. 단기 급등 후 조정세.</t>
+          <t>차세대 광반도체 및 광통신 관련 기대감 상승. SK하이닉스 CPO 광원 이슈 연관성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2900</v>
+        <v>2890</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.69%</t>
+          <t>+10.31%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-2.39</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H4" t="n">
         <v>1.44</v>
@@ -794,7 +794,7 @@
         <v>3.83</v>
       </c>
       <c r="O4" t="n">
-        <v>81611069924</v>
+        <v>82545444526</v>
       </c>
       <c r="P4" t="n">
         <v>4810</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17150</v>
+        <v>17120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+6.79%</t>
+          <t>+6.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H5" t="n">
         <v>2.7</v>
@@ -886,7 +886,7 @@
         <v>2.39</v>
       </c>
       <c r="O5" t="n">
-        <v>227747252720</v>
+        <v>229269807845</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 보안 관련주로 2연상 기록, AI 개발 속도 조절론에도 불구하고 상승세 지속. 양자 보안 기대감.</t>
+          <t>AI 개발 속도 조절론에 따른 우려와 기대감이 혼재. 양자 보안 테마 연관성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI보안', '양자보안', '2연상']</t>
+          <t>['AI', '양자보안', '속도조절론']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15020</v>
+        <v>14880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2.81%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.97</v>
       </c>
       <c r="E6" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G6" t="n">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="H6" t="n">
         <v>1.17</v>
@@ -978,7 +978,7 @@
         <v>3.14</v>
       </c>
       <c r="O6" t="n">
-        <v>86036243540</v>
+        <v>87794091765</v>
       </c>
       <c r="P6" t="n">
         <v>36200</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국제 유가 상승세 속에서 지정학적 리스크 부각. 다만, 외인·기관·프로그램 매도세 관찰.</t>
+          <t>중동 회담 연기로 인한 국제유가 상승 기대감. 다만, 외인·기관 매도세 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈해협', '지정학적리스크']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8340</v>
+        <v>8320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.54</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G7" t="n">
-        <v>601</v>
+        <v>632</v>
       </c>
       <c r="H7" t="n">
         <v>0.75</v>
@@ -1070,7 +1070,7 @@
         <v>1.29</v>
       </c>
       <c r="O7" t="n">
-        <v>17621079710</v>
+        <v>17844692760</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>항암 신약 개발 기대감 속 임상 결과 주목. 글로벌 심포지엄 개최 및 탑급 교수진 발표 예정.</t>
+          <t>항암 치료 바이오 신약 관련 글로벌 심포지엄 개최 뉴스 및 임상 결과 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['항암신약', '임상결과', '바이오']</t>
+          <t>['항암', '바이오 신약', '임상 결과']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14180</v>
+        <v>14160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
         <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="H8" t="n">
         <v>1.88</v>
@@ -1162,7 +1162,7 @@
         <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>58667840275</v>
+        <v>60274356810</v>
       </c>
       <c r="P8" t="n">
         <v>31500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>AI 성장 기대감 속 광통신 기술력 주목. 일부 투자자 프로그램 매수세 관찰.</t>
+          <t>GPU 확보 관련 긍정적 뉴스 언급, 금리 유지 기대감 속 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '기술력']</t>
+          <t>['GPU', '광통신', 'AIDC']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11880</v>
+        <v>1852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.51</v>
+        <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>97</v>
+        <v>184</v>
       </c>
       <c r="H9" t="n">
-        <v>17.58</v>
+        <v>2.08</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11950</v>
+        <v>1878</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1909</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1961</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1848</v>
       </c>
       <c r="N9" t="n">
-        <v>17.07</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>48860000000</v>
+        <v>13253467479</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4795</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1524</v>
       </c>
       <c r="R9" t="n">
-        <v>69000</v>
+        <v>-192000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 급등주로 거래량 폭증, 외인 수급 변동성과 함께 투자 주의 의견 제기. 추석 전 상승 기대.</t>
+          <t>홍해 및 호르무즈 해협 불안정으로 인한 유조선 운임 상승 기대. 다만, 해운주 악재 및 국제유가 상승으로 인한 원가 상승 우려도 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['단타', '수급', '전환사채']</t>
+          <t>['홍해', '호르무즈', '운임']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,182 +1292,182 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1859</v>
+        <v>12050</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.36</v>
+        <v>-0.72</v>
       </c>
       <c r="E10" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
         <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>166</v>
+        <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>0.22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1878</v>
+        <v>12290</v>
       </c>
       <c r="K10" t="n">
-        <v>1909</v>
+        <v>12030</v>
       </c>
       <c r="L10" t="n">
-        <v>1961</v>
+        <v>13230</v>
       </c>
       <c r="M10" t="n">
-        <v>1851</v>
+        <v>11820</v>
       </c>
       <c r="N10" t="n">
-        <v>2.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>12812992248</v>
+        <v>50661573885</v>
       </c>
       <c r="P10" t="n">
-        <v>4795</v>
+        <v>20850</v>
       </c>
       <c r="Q10" t="n">
-        <v>1524</v>
+        <v>4020</v>
       </c>
       <c r="R10" t="n">
-        <v>-192000</v>
+        <v>30000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>홍해 및 호르무즈 해협 불안으로 인한 유조선 운임 상승 전망. 전쟁 테마 관련 언급. 유가 상승으로 인한 원가 상승 우려.</t>
+          <t>원전주 폭락 속 종목 자체에 대한 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['운임', '유가', '전쟁 테마']</t>
+          <t>['원전주', '폭락', '거래량']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11950</v>
+        <v>87900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.77%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.72</v>
+        <v>-0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="G11" t="n">
-        <v>29</v>
+        <v>507</v>
       </c>
       <c r="H11" t="n">
-        <v>0.22</v>
+        <v>23.56</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>12290</v>
+        <v>90800</v>
       </c>
       <c r="K11" t="n">
-        <v>12030</v>
+        <v>89800</v>
       </c>
       <c r="L11" t="n">
-        <v>13230</v>
+        <v>90400</v>
       </c>
       <c r="M11" t="n">
-        <v>11820</v>
+        <v>87700</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9399999999999999</v>
+        <v>23.59</v>
       </c>
       <c r="O11" t="n">
-        <v>49917472185</v>
+        <v>116515571800</v>
       </c>
       <c r="P11" t="n">
-        <v>20850</v>
+        <v>139200</v>
       </c>
       <c r="Q11" t="n">
-        <v>4020</v>
+        <v>57000</v>
       </c>
       <c r="R11" t="n">
-        <v>30000</v>
+        <v>-320000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-89000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>원전주 폭락세 속 개별 이슈 부재. 거래량은 양호하나 주가 하락세 지속.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 기대감, 기관 매수세 및 공매도와의 공방.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '거래량']</t>
+          <t>['원전', '국제유가', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>87900</v>
+        <v>12000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>0.51</v>
       </c>
       <c r="E12" t="n">
-        <v>161</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>498</v>
+        <v>104</v>
       </c>
       <c r="H12" t="n">
-        <v>23.56</v>
+        <v>17.58</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>90800</v>
+        <v>12450</v>
       </c>
       <c r="K12" t="n">
-        <v>89800</v>
+        <v>11960</v>
       </c>
       <c r="L12" t="n">
-        <v>90400</v>
+        <v>13900</v>
       </c>
       <c r="M12" t="n">
-        <v>87700</v>
+        <v>11810</v>
       </c>
       <c r="N12" t="n">
-        <v>23.59</v>
+        <v>17.07</v>
       </c>
       <c r="O12" t="n">
-        <v>111161042700</v>
+        <v>49795780730</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>14350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>465</v>
       </c>
       <c r="R12" t="n">
-        <v>-320000</v>
+        <v>69000</v>
       </c>
       <c r="S12" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 기대감, 기관 매수세 및 공매도와의 공방.</t>
+          <t>거래량 증가 및 외인 매수세 유입에 따른 상승 기대감 표출. 다만, 전환사채 관련 부정적 언급도 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '국제유가', '기관']</t>
+          <t>['거래량', '외인매수', '전환사채']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G13" t="n">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="H13" t="n">
         <v>46.64</v>
@@ -1622,7 +1622,7 @@
         <v>46.71</v>
       </c>
       <c r="O13" t="n">
-        <v>1344900262250</v>
+        <v>1436009718000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈와 맞물려 부정적인 시장 전망 및 반도체 업황에 대한 우려 제기.</t>
+          <t>정치적 이슈에 대한 언급이 주를 이루며, 특정 정치인 관련 부정적 의견 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '반도체', '시장']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18790</v>
+        <v>18900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>32</v>
       </c>
       <c r="G14" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="H14" t="n">
         <v>10.55</v>
@@ -1714,7 +1714,7 @@
         <v>10.65</v>
       </c>
       <c r="O14" t="n">
-        <v>38704292445</v>
+        <v>40461132885</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차해지 운동 관련 논의가 활발하며, 저점 상승 추세 및 미국 증시 동반 상승 기대감.</t>
+          <t>대차해지 운동에 대한 독려가 주를 이루며, 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '주주운동', '저점']</t>
+          <t>['대차해지', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1695000</v>
+        <v>1715000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-6.46%</t>
+          <t>-5.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="G15" t="n">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="H15" t="n">
         <v>50.47</v>
@@ -1806,7 +1806,7 @@
         <v>50.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2600572503500</v>
+        <v>2780109256500</v>
       </c>
       <c r="P15" t="n">
         <v>2987000</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 및 정치적 이슈로 인한 하락세, 현금 보유 및 관망세 짙어짐.</t>
+          <t>반도체 업황 악화 우려 및 부정적 전망 제기. 공매도 금지 청원 및 트럼프 관련 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '업황', '하락']</t>
+          <t>['반도체', '공매도', '업황']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13730</v>
+        <v>13840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-6.66%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         <v>15420</v>
       </c>
       <c r="M16" t="n">
-        <v>13710</v>
+        <v>13700</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>22152811860</v>
+        <v>22712487335</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 호재에도 불구하고, 주가 하락세 및 공사비 증가 우려.</t>
+          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고 하락세 우려 및 부정적 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['재건축', '시공사', '공사비']</t>
+          <t>['재건축', '시공사']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20260914_10.xlsx
+++ b/data/trending_integrated_20260914_10.xlsx
@@ -567,21 +567,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6810</v>
+        <v>6650</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.59%</t>
+          <t>+20.69%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
         <v>73</v>
@@ -610,7 +610,7 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>43210945485</v>
+        <v>44209105610</v>
       </c>
       <c r="P2" t="n">
         <v>10360</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9080</v>
+        <v>9480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+14.94%</t>
+          <t>+20.00%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.28</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
         <v>17.67</v>
@@ -702,7 +702,7 @@
         <v>17.95</v>
       </c>
       <c r="O3" t="n">
-        <v>126915670200</v>
+        <v>143844290775</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련 기대감 상승. SK하이닉스 CPO 광원 이슈 연관성 언급.</t>
+          <t>차세대 광반도체 및 광통신 관련 기대감 속 텐버거 가능성 언급. 주가 상승 및 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', 'CPO']</t>
+          <t>['광반도체', '광통신', '텐버거']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2890</v>
+        <v>2850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.31%</t>
+          <t>+8.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H4" t="n">
         <v>1.44</v>
@@ -794,7 +794,7 @@
         <v>3.83</v>
       </c>
       <c r="O4" t="n">
-        <v>82545444526</v>
+        <v>83506036166</v>
       </c>
       <c r="P4" t="n">
         <v>4810</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17120</v>
+        <v>17000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+6.60%</t>
+          <t>+5.85%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H5" t="n">
         <v>2.7</v>
@@ -886,7 +886,7 @@
         <v>2.39</v>
       </c>
       <c r="O5" t="n">
-        <v>229269807845</v>
+        <v>231489793720</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론에 따른 우려와 기대감이 혼재. 양자 보안 테마 연관성 언급.</t>
+          <t>AI 개발 속도 조절론 부상과 양자 보안 테마 관련 주가 상승 기대. 매물대 정리 및 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '양자보안', '속도조절론']</t>
+          <t>['AI', '양자보안', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14880</v>
+        <v>14360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.97</v>
+        <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>195</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>504</v>
+        <v>348</v>
       </c>
       <c r="H6" t="n">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14610</v>
+        <v>14150</v>
       </c>
       <c r="K6" t="n">
-        <v>15420</v>
+        <v>13850</v>
       </c>
       <c r="L6" t="n">
-        <v>16510</v>
+        <v>14530</v>
       </c>
       <c r="M6" t="n">
-        <v>14720</v>
+        <v>13800</v>
       </c>
       <c r="N6" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>87794091765</v>
+        <v>62226296765</v>
       </c>
       <c r="P6" t="n">
-        <v>36200</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>8920</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>-23000</v>
+        <v>-356000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>중동 회담 연기로 인한 국제유가 상승 기대감. 다만, 외인·기관 매도세 관찰.</t>
+          <t>GPU 확보 관련 긍정적 뉴스 언급, 금리 유지 기대감 속 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['GPU', '광통신', 'AIDC']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8320</v>
+        <v>8390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.54</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>632</v>
+        <v>656</v>
       </c>
       <c r="H7" t="n">
         <v>0.75</v>
@@ -1070,7 +1070,7 @@
         <v>1.29</v>
       </c>
       <c r="O7" t="n">
-        <v>17844692760</v>
+        <v>18060061880</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>항암 치료 바이오 신약 관련 글로벌 심포지엄 개최 뉴스 및 임상 결과 기대감.</t>
+          <t>페니트리움바이오, ‘가짜내성’ 타깃 항암 전략 제시로 글로벌 심포지엄 개최. 암 치료 신약 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['항암', '바이오 신약', '임상 결과']</t>
+          <t>['항암 전략', '글로벌 심포지엄', '암 치료']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14160</v>
+        <v>14740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.62</v>
+        <v>-1.97</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>115</v>
       </c>
       <c r="G8" t="n">
-        <v>345</v>
+        <v>526</v>
       </c>
       <c r="H8" t="n">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14150</v>
+        <v>14610</v>
       </c>
       <c r="K8" t="n">
-        <v>13850</v>
+        <v>15420</v>
       </c>
       <c r="L8" t="n">
-        <v>14530</v>
+        <v>16510</v>
       </c>
       <c r="M8" t="n">
-        <v>13800</v>
+        <v>14690</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="O8" t="n">
-        <v>60274356810</v>
+        <v>89540527205</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>36200</v>
       </c>
       <c r="Q8" t="n">
-        <v>1272</v>
+        <v>8920</v>
       </c>
       <c r="R8" t="n">
-        <v>-356000</v>
+        <v>-23000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>GPU 확보 관련 긍정적 뉴스 언급, 금리 유지 기대감 속 프로그램 매수세 확인.</t>
+          <t>중동 회담 연기로 인한 국제유가 상승 기대감. 다만, 외인·기관 매도세 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['GPU', '광통신', 'AIDC']</t>
+          <t>['국제유가', '호르무즈', '회담연기']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,7 +1225,7 @@
         <v>43</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
         <v>184</v>
@@ -1254,7 +1254,7 @@
         <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>13253467479</v>
+        <v>13389054085</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홍해 및 호르무즈 해협 불안정으로 인한 유조선 운임 상승 기대. 다만, 해운주 악재 및 국제유가 상승으로 인한 원가 상승 우려도 공존.</t>
+          <t>홍해 사태 및 유가 상승으로 인한 운임 상승 기대와 해운주 악재(원가 상승) 공존. 주가 상승 및 하락 논쟁.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['홍해', '호르무즈', '운임']</t>
+          <t>['홍해', '유가', '운임']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12050</v>
+        <v>12010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.72</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H10" t="n">
         <v>0.22</v>
@@ -1346,7 +1346,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>50661573885</v>
+        <v>50967978760</v>
       </c>
       <c r="P10" t="n">
         <v>20850</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전주 폭락 속 종목 자체에 대한 부정적 언급 다수.</t>
+          <t>원전주 폭락 및 차트 붕괴에 따른 투자 심리 위축. 주가 하락 및 불안정한 흐름 지속.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전주', '폭락', '거래량']</t>
+          <t>['원전', '폭락', '차트']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87900</v>
+        <v>88150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>170</v>
       </c>
       <c r="F11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G11" t="n">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="H11" t="n">
         <v>23.56</v>
@@ -1438,7 +1438,7 @@
         <v>23.59</v>
       </c>
       <c r="O11" t="n">
-        <v>116515571800</v>
+        <v>119187909700</v>
       </c>
       <c r="P11" t="n">
         <v>139200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 기대감, 기관 매수세 및 공매도와의 공방.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 가능성 및 기관 매수세 유입 기대. 공매도 세력과의 기관 매집 공방.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '국제유가', '기관']</t>
+          <t>['원전', '유가', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12000</v>
+        <v>250250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.61%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.51</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>510</v>
       </c>
       <c r="G12" t="n">
-        <v>104</v>
+        <v>1733</v>
       </c>
       <c r="H12" t="n">
-        <v>17.58</v>
+        <v>46.64</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12450</v>
+        <v>259500</v>
       </c>
       <c r="K12" t="n">
-        <v>11960</v>
+        <v>249500</v>
       </c>
       <c r="L12" t="n">
-        <v>13900</v>
+        <v>252500</v>
       </c>
       <c r="M12" t="n">
-        <v>11810</v>
+        <v>249000</v>
       </c>
       <c r="N12" t="n">
-        <v>17.07</v>
+        <v>46.71</v>
       </c>
       <c r="O12" t="n">
-        <v>49795780730</v>
+        <v>1523912972750</v>
       </c>
       <c r="P12" t="n">
-        <v>14350</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>465</v>
+        <v>75900</v>
       </c>
       <c r="R12" t="n">
-        <v>69000</v>
+        <v>-1189000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-852000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>거래량 증가 및 외인 매수세 유입에 따른 상승 기대감 표출. 다만, 전환사채 관련 부정적 언급도 존재.</t>
+          <t>정치적 이슈와 연계된 부정적 전망 및 하락 위기감 고조. 시장 전반의 불안감 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['거래량', '외인매수', '전환사채']</t>
+          <t>['대통령', '경제', '하락']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>249500</v>
+        <v>11890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.50%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>62</v>
       </c>
       <c r="F13" t="n">
-        <v>520</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>1715</v>
+        <v>109</v>
       </c>
       <c r="H13" t="n">
-        <v>46.64</v>
+        <v>17.58</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>259500</v>
+        <v>12450</v>
       </c>
       <c r="K13" t="n">
-        <v>249500</v>
+        <v>11960</v>
       </c>
       <c r="L13" t="n">
-        <v>252500</v>
+        <v>13900</v>
       </c>
       <c r="M13" t="n">
-        <v>249000</v>
+        <v>11810</v>
       </c>
       <c r="N13" t="n">
-        <v>46.71</v>
+        <v>17.07</v>
       </c>
       <c r="O13" t="n">
-        <v>1436009718000</v>
+        <v>50721815140</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>14350</v>
       </c>
       <c r="Q13" t="n">
-        <v>75900</v>
+        <v>465</v>
       </c>
       <c r="R13" t="n">
-        <v>-1189000</v>
+        <v>69000</v>
       </c>
       <c r="S13" t="n">
-        <v>-852000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 이슈에 대한 언급이 주를 이루며, 특정 정치인 관련 부정적 의견 다수.</t>
+          <t>외인 매수세 유입에 따른 주가 상승 기대감과 급등 가능성 언급. 투자 경고 및 주의에 대한 우려.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['외인', '매수', '급등']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18900</v>
+        <v>1721000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>532</v>
       </c>
       <c r="G14" t="n">
-        <v>232</v>
+        <v>1276</v>
       </c>
       <c r="H14" t="n">
-        <v>10.55</v>
+        <v>50.47</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19890</v>
+        <v>1812000</v>
       </c>
       <c r="K14" t="n">
-        <v>19480</v>
+        <v>1707000</v>
       </c>
       <c r="L14" t="n">
-        <v>19550</v>
+        <v>1729000</v>
       </c>
       <c r="M14" t="n">
-        <v>18780</v>
+        <v>1695000</v>
       </c>
       <c r="N14" t="n">
-        <v>10.65</v>
+        <v>50.55</v>
       </c>
       <c r="O14" t="n">
-        <v>40461132885</v>
+        <v>2939471261000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>325000</v>
       </c>
       <c r="R14" t="n">
-        <v>-224000</v>
+        <v>-662000</v>
       </c>
       <c r="S14" t="n">
-        <v>5000</v>
+        <v>-142000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대차해지 운동에 대한 독려가 주를 이루며, 공매도 관련 부정적 언급.</t>
+          <t>반도체 시장 약세 및 주가 하락 우려 속에 현금 보유 및 관망세 촉구. 개인 투자자들의 어려움 토로.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도']</t>
+          <t>['반도체', '하락', '현금보유']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1715000</v>
+        <v>18870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-5.35%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>524</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>1311</v>
+        <v>230</v>
       </c>
       <c r="H15" t="n">
-        <v>50.47</v>
+        <v>10.55</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1812000</v>
+        <v>19890</v>
       </c>
       <c r="K15" t="n">
-        <v>1707000</v>
+        <v>19480</v>
       </c>
       <c r="L15" t="n">
-        <v>1729000</v>
+        <v>19550</v>
       </c>
       <c r="M15" t="n">
-        <v>1695000</v>
+        <v>18780</v>
       </c>
       <c r="N15" t="n">
-        <v>50.55</v>
+        <v>10.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2780109256500</v>
+        <v>41756433100</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>325000</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-662000</v>
+        <v>-224000</v>
       </c>
       <c r="S15" t="n">
-        <v>-142000</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>반도체 업황 악화 우려 및 부정적 전망 제기. 공매도 금지 청원 및 트럼프 관련 언급.</t>
+          <t>대차 해지 운동을 통한 공매도 세력 대응 촉구. 주가 하락 방어 및 반등 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['반도체', '공매도', '업황']</t>
+          <t>['대차해지', '공매도', '주주운동']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13840</v>
+        <v>13795</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-6.22%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>22712487335</v>
+        <v>23184791865</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고 하락세 우려 및 부정적 전망.</t>
+          <t>수주 소식에도 불구하고 주가 하락 및 투자 심리 위축. 재건축 사업 시공사 선정 등 긍정적 뉴스에도 부정적 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['재건축', '시공사']</t>
+          <t>['수주', '재건축', '하락']</t>
         </is>
       </c>
       <c r="X16" t="n">

--- a/data/trending_integrated_20260914_10.xlsx
+++ b/data/trending_integrated_20260914_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6650</v>
+        <v>6740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+20.69%</t>
+          <t>+22.32%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.01</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H2" t="n">
         <v>1.67</v>
@@ -610,7 +610,7 @@
         <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>44209105610</v>
+        <v>44684589975</v>
       </c>
       <c r="P2" t="n">
         <v>10360</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 보안 및 딥페이크 대장주로서의 기대감 표출. 투경 및 단일가 예고 언급.</t>
+          <t>AI 보안 및 딥페이크 관련주로 언급되나, 차익 실현 매물 및 단기 급등 가능성에 대한 경계 심리 존재.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI보안', '딥페이크', '대장주']</t>
+          <t>['AI 보안', '딥페이크', '단기 급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9480</v>
+        <v>9450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.00%</t>
+          <t>+19.62%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.28</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H3" t="n">
         <v>17.67</v>
@@ -693,7 +693,7 @@
         <v>7790</v>
       </c>
       <c r="L3" t="n">
-        <v>9500</v>
+        <v>9650</v>
       </c>
       <c r="M3" t="n">
         <v>7700</v>
@@ -702,7 +702,7 @@
         <v>17.95</v>
       </c>
       <c r="O3" t="n">
-        <v>143844290775</v>
+        <v>163773548925</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>차세대 광반도체 및 광통신 관련 기대감 속 텐버거 가능성 언급. 주가 상승 및 전고점 돌파 전망.</t>
+          <t>차세대 광반도체, 광통신 관련주로 부각되며 프로그램 및 주포의 매수세 유입 기대. 3분봉 패턴 및 거래량 증가 확인, 매물대 돌파 시도.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광반도체', '광통신', '텐버거']</t>
+          <t>['광반도체', '광통신', '매물대']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>드림시큐리티</t>
+          <t>삼익제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2850</v>
+        <v>8940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+8.78%</t>
+          <t>+13.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-2.39</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="H4" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2620</v>
+        <v>7910</v>
       </c>
       <c r="K4" t="n">
-        <v>2745</v>
+        <v>7800</v>
       </c>
       <c r="L4" t="n">
-        <v>3145</v>
+        <v>9840</v>
       </c>
       <c r="M4" t="n">
-        <v>2700</v>
+        <v>7540</v>
       </c>
       <c r="N4" t="n">
-        <v>3.83</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>83506036166</v>
+        <v>51567471855</v>
       </c>
       <c r="P4" t="n">
-        <v>4810</v>
+        <v>25050</v>
       </c>
       <c r="Q4" t="n">
-        <v>1400</v>
+        <v>3705</v>
       </c>
       <c r="R4" t="n">
-        <v>-309000</v>
+        <v>16000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>양자보안 대장주로 부각되며, 매출액 증가 및 전고점 돌파 기대감. 투자경고 조건 충족 시 매도 고려.</t>
+          <t>월 1회 주사 가능한 펩타이드 면역조절 기술 국내 특허 등록, 비만 치료제 확장 가능성에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['양자보안', '매출액', '대장주']</t>
+          <t>['펩타이드', '특허 등록', '면역 조절']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>203650</t>
+          <t>014950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>엑스게이트</t>
+          <t>파인엠텍</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17000</v>
+        <v>9210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+5.85%</t>
+          <t>+11.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.31</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7</v>
+        <v>0.83</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16060</v>
+        <v>8290</v>
       </c>
       <c r="K5" t="n">
-        <v>16780</v>
+        <v>8300</v>
       </c>
       <c r="L5" t="n">
-        <v>18610</v>
+        <v>9425</v>
       </c>
       <c r="M5" t="n">
-        <v>16230</v>
+        <v>8300</v>
       </c>
       <c r="N5" t="n">
-        <v>2.39</v>
+        <v>0.82</v>
       </c>
       <c r="O5" t="n">
-        <v>231489793720</v>
+        <v>28681219955</v>
       </c>
       <c r="P5" t="n">
-        <v>30550</v>
+        <v>12800</v>
       </c>
       <c r="Q5" t="n">
-        <v>6100</v>
+        <v>5340</v>
       </c>
       <c r="R5" t="n">
-        <v>-135000</v>
+        <v>353000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>99000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>AI 개발 속도 조절론 부상과 양자 보안 테마 관련 주가 상승 기대. 매물대 정리 및 추가 상승 전망.</t>
+          <t>폴더블폰 시장 확대에 따른 수혜 기대감, 그러나 단기 차익 실현 및 전환사채 관련 이슈로 인한 변동성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['AI', '양자보안', '상승']</t>
+          <t>['폴더블', '매출 증', '전환사채']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>356680</t>
+          <t>441270</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>드림시큐리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14360</v>
+        <v>2855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+8.97%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.62</v>
+        <v>-2.39</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>348</v>
+        <v>141</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14150</v>
+        <v>2620</v>
       </c>
       <c r="K6" t="n">
-        <v>13850</v>
+        <v>2745</v>
       </c>
       <c r="L6" t="n">
-        <v>14530</v>
+        <v>3145</v>
       </c>
       <c r="M6" t="n">
-        <v>13800</v>
+        <v>2700</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>62226296765</v>
+        <v>85162213559</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>4810</v>
       </c>
       <c r="Q6" t="n">
-        <v>1272</v>
+        <v>1400</v>
       </c>
       <c r="R6" t="n">
-        <v>-356000</v>
+        <v>-309000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>GPU 확보 관련 긍정적 뉴스 언급, 금리 유지 기대감 속 프로그램 매수세 확인.</t>
+          <t>양자 보안 관련주로 부각되며 강한 상승세 시현. 매출액 및 영업이익 증가 추세, 4800원 전고점 돌파 기대. 투경 조건 진입 시 매도 권고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['GPU', '광통신', 'AIDC']</t>
+          <t>['양자 보안', '매출액', '전고점 돌파']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>203650</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>엑스게이트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8390</v>
+        <v>17090</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>+6.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.54</v>
+        <v>0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>656</v>
+        <v>122</v>
       </c>
       <c r="H7" t="n">
-        <v>0.75</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8290</v>
+        <v>16060</v>
       </c>
       <c r="K7" t="n">
-        <v>8100</v>
+        <v>16780</v>
       </c>
       <c r="L7" t="n">
-        <v>9050</v>
+        <v>18610</v>
       </c>
       <c r="M7" t="n">
-        <v>8060</v>
+        <v>16230</v>
       </c>
       <c r="N7" t="n">
-        <v>1.29</v>
+        <v>2.39</v>
       </c>
       <c r="O7" t="n">
-        <v>18060061880</v>
+        <v>234175919405</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>30550</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>6100</v>
       </c>
       <c r="R7" t="n">
-        <v>77000</v>
+        <v>-135000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>페니트리움바이오, ‘가짜내성’ 타깃 항암 전략 제시로 글로벌 심포지엄 개최. 암 치료 신약 관련 기대감 형성.</t>
+          <t>AI 개발 속도 조절론에도 불구하고 양자 보안 테마 부각 및 2연상 시현. 17층 매물대 정리 및 주가 상승 지속, 18200원 매수세 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['항암 전략', '글로벌 심포지엄', '암 치료']</t>
+          <t>['양자 보안', 'AI', '2연상']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>356680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14740</v>
+        <v>3975</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.97</v>
+        <v>-0.45</v>
       </c>
       <c r="E8" t="n">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>526</v>
+        <v>66</v>
       </c>
       <c r="H8" t="n">
-        <v>1.17</v>
+        <v>0.59</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14610</v>
+        <v>3870</v>
       </c>
       <c r="K8" t="n">
-        <v>15420</v>
+        <v>3860</v>
       </c>
       <c r="L8" t="n">
-        <v>16510</v>
+        <v>4135</v>
       </c>
       <c r="M8" t="n">
-        <v>14690</v>
+        <v>3740</v>
       </c>
       <c r="N8" t="n">
-        <v>3.14</v>
+        <v>1.04</v>
       </c>
       <c r="O8" t="n">
-        <v>89540527205</v>
+        <v>66623962050</v>
       </c>
       <c r="P8" t="n">
-        <v>36200</v>
+        <v>8100</v>
       </c>
       <c r="Q8" t="n">
-        <v>8920</v>
+        <v>592</v>
       </c>
       <c r="R8" t="n">
-        <v>-23000</v>
+        <v>-153000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>중동 회담 연기로 인한 국제유가 상승 기대감. 다만, 외인·기관 매도세 관찰.</t>
+          <t>GPU, 광통신, AIDC 관련 기술 성장 기대감 속에 주가 상승. 프로그램 매수세 유입 및 추세적 상승 전망, 4150원 평단가 대비 목표가 7500원 제시.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국제유가', '호르무즈', '회담연기']</t>
+          <t>['광통신', 'AIDC', '추세적 상승']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1855</v>
+        <v>8490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.36</v>
+        <v>-0.54</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>184</v>
+        <v>663</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>0.75</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1878</v>
+        <v>8290</v>
       </c>
       <c r="K9" t="n">
-        <v>1909</v>
+        <v>8100</v>
       </c>
       <c r="L9" t="n">
-        <v>1961</v>
+        <v>9050</v>
       </c>
       <c r="M9" t="n">
-        <v>1848</v>
+        <v>8060</v>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>1.29</v>
       </c>
       <c r="O9" t="n">
-        <v>13389054085</v>
+        <v>18664864345</v>
       </c>
       <c r="P9" t="n">
-        <v>4795</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1524</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>-192000</v>
+        <v>77000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>홍해 사태 및 유가 상승으로 인한 운임 상승 기대와 해운주 악재(원가 상승) 공존. 주가 상승 및 하락 논쟁.</t>
+          <t>페니트리움바이오, ‘가짜내성’ 타깃 항암 전략 제시로 글로벌 심포지엄 개최. 암 치료 신약 관련 기대감 형성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['홍해', '유가', '운임']</t>
+          <t>['항암 전략', '글로벌 심포지엄', '암 치료']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12010</v>
+        <v>14410</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.28%</t>
+          <t>+1.84%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.72</v>
+        <v>-0.62</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>349</v>
       </c>
       <c r="H10" t="n">
-        <v>0.22</v>
+        <v>1.88</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12290</v>
+        <v>14150</v>
       </c>
       <c r="K10" t="n">
-        <v>12030</v>
+        <v>13850</v>
       </c>
       <c r="L10" t="n">
-        <v>13230</v>
+        <v>14530</v>
       </c>
       <c r="M10" t="n">
-        <v>11820</v>
+        <v>13800</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>50967978760</v>
+        <v>65611744030</v>
       </c>
       <c r="P10" t="n">
-        <v>20850</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>4020</v>
+        <v>1272</v>
       </c>
       <c r="R10" t="n">
-        <v>30000</v>
+        <v>-356000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>원전주 폭락 및 차트 붕괴에 따른 투자 심리 위축. 주가 하락 및 불안정한 흐름 지속.</t>
+          <t>GPU 확보 관련 긍정적 뉴스 언급, 금리 유지 기대감 속 프로그램 매수세 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '폭락', '차트']</t>
+          <t>['GPU', '광통신', 'AIDC']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88150</v>
+        <v>14750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.03</v>
+        <v>-1.97</v>
       </c>
       <c r="E11" t="n">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="F11" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G11" t="n">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="H11" t="n">
-        <v>23.56</v>
+        <v>1.17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>90800</v>
+        <v>14610</v>
       </c>
       <c r="K11" t="n">
-        <v>89800</v>
+        <v>15420</v>
       </c>
       <c r="L11" t="n">
-        <v>90400</v>
+        <v>16510</v>
       </c>
       <c r="M11" t="n">
-        <v>87700</v>
+        <v>14690</v>
       </c>
       <c r="N11" t="n">
-        <v>23.59</v>
+        <v>3.14</v>
       </c>
       <c r="O11" t="n">
-        <v>119187909700</v>
+        <v>90724439525</v>
       </c>
       <c r="P11" t="n">
-        <v>139200</v>
+        <v>36200</v>
       </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>8920</v>
       </c>
       <c r="R11" t="n">
-        <v>-320000</v>
+        <v>-23000</v>
       </c>
       <c r="S11" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국제 유가 상승에 따른 원전주 상승 가능성 및 기관 매수세 유입 기대. 공매도 세력과의 기관 매집 공방.</t>
+          <t>이란-걸프 국가 회담 연기 및 국제 유가 상승에 따른 수혜 기대감, 그러나 외인/기관 매도세로 인한 변동성 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '유가', '기관']</t>
+          <t>['국제 유가', '회담 연기', '흥구석유']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>250250</v>
+        <v>1860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.36</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>510</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>1733</v>
+        <v>181</v>
       </c>
       <c r="H12" t="n">
-        <v>46.64</v>
+        <v>2.08</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>259500</v>
+        <v>1878</v>
       </c>
       <c r="K12" t="n">
-        <v>249500</v>
+        <v>1909</v>
       </c>
       <c r="L12" t="n">
-        <v>252500</v>
+        <v>1961</v>
       </c>
       <c r="M12" t="n">
-        <v>249000</v>
+        <v>1848</v>
       </c>
       <c r="N12" t="n">
-        <v>46.71</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1523912972750</v>
+        <v>13517338063</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>4795</v>
       </c>
       <c r="Q12" t="n">
-        <v>75900</v>
+        <v>1524</v>
       </c>
       <c r="R12" t="n">
-        <v>-1189000</v>
+        <v>-192000</v>
       </c>
       <c r="S12" t="n">
-        <v>-852000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 부정적 전망 및 하락 위기감 고조. 시장 전반의 불안감 표출.</t>
+          <t>유가 상승 및 중동 불안 심화로 인한 운임 강세 기대에도 불구하고, 해운주 전반의 악재 및 매수세 부진으로 주가 부진. 원가 상승 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대통령', '경제', '하락']</t>
+          <t>['유가', '운임', '중동 불안']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호전기</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11890</v>
+        <v>11990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.50%</t>
+          <t>-2.44%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.51</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>17.58</v>
+        <v>0.22</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12450</v>
+        <v>12290</v>
       </c>
       <c r="K13" t="n">
-        <v>11960</v>
+        <v>12030</v>
       </c>
       <c r="L13" t="n">
-        <v>13900</v>
+        <v>13230</v>
       </c>
       <c r="M13" t="n">
-        <v>11810</v>
+        <v>11820</v>
       </c>
       <c r="N13" t="n">
-        <v>17.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>50721815140</v>
+        <v>51231656795</v>
       </c>
       <c r="P13" t="n">
-        <v>14350</v>
+        <v>20850</v>
       </c>
       <c r="Q13" t="n">
-        <v>465</v>
+        <v>4020</v>
       </c>
       <c r="R13" t="n">
-        <v>69000</v>
+        <v>30000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에 따른 주가 상승 기대감과 급등 가능성 언급. 투자 경고 및 주의에 대한 우려.</t>
+          <t>원전주 전반의 하락세 및 재료 소멸 가능성 언급, 보유 물량 관리 및 신규 진입에 대한 보수적 관점.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외인', '매수', '급등']</t>
+          <t>['원전주', '폭락', '재료 소멸']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>001210</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1721000</v>
+        <v>88200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>171</v>
       </c>
       <c r="F14" t="n">
-        <v>532</v>
+        <v>101</v>
       </c>
       <c r="G14" t="n">
-        <v>1276</v>
+        <v>533</v>
       </c>
       <c r="H14" t="n">
-        <v>50.47</v>
+        <v>23.56</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1812000</v>
+        <v>90800</v>
       </c>
       <c r="K14" t="n">
-        <v>1707000</v>
+        <v>89800</v>
       </c>
       <c r="L14" t="n">
-        <v>1729000</v>
+        <v>90400</v>
       </c>
       <c r="M14" t="n">
-        <v>1695000</v>
+        <v>87700</v>
       </c>
       <c r="N14" t="n">
-        <v>50.55</v>
+        <v>23.59</v>
       </c>
       <c r="O14" t="n">
-        <v>2939471261000</v>
+        <v>122774229050</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>325000</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-662000</v>
+        <v>-320000</v>
       </c>
       <c r="S14" t="n">
-        <v>-142000</v>
+        <v>-89000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 시장 약세 및 주가 하락 우려 속에 현금 보유 및 관망세 촉구. 개인 투자자들의 어려움 토로.</t>
+          <t>국제 유가 상승에 따른 원전주 상승 가능성 및 기관 매수세 유입 기대. 공매도 세력과의 기관 매집 공방.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '하락', '현금보유']</t>
+          <t>['원전', '유가', '기관']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18870</v>
+        <v>250250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-5.13%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>512</v>
       </c>
       <c r="G15" t="n">
-        <v>230</v>
+        <v>1738</v>
       </c>
       <c r="H15" t="n">
-        <v>10.55</v>
+        <v>46.64</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19890</v>
+        <v>259500</v>
       </c>
       <c r="K15" t="n">
-        <v>19480</v>
+        <v>249500</v>
       </c>
       <c r="L15" t="n">
-        <v>19550</v>
+        <v>252500</v>
       </c>
       <c r="M15" t="n">
-        <v>18780</v>
+        <v>249000</v>
       </c>
       <c r="N15" t="n">
-        <v>10.65</v>
+        <v>46.71</v>
       </c>
       <c r="O15" t="n">
-        <v>41756433100</v>
+        <v>1618310947250</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>75900</v>
       </c>
       <c r="R15" t="n">
-        <v>-224000</v>
+        <v>-1189000</v>
       </c>
       <c r="S15" t="n">
-        <v>5000</v>
+        <v>-852000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대차 해지 운동을 통한 공매도 세력 대응 촉구. 주가 하락 방어 및 반등 기대.</t>
+          <t>국내 증시 전반의 하락세 및 외국인/기관 매도세 심화 속에 주가 급락. 정치적 이슈 및 부정적 전망이 투자 심리 악화.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대차해지', '공매도', '주주운동']</t>
+          <t>['주가 급락', '외국인 매도', '투자 심리']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13795</v>
+        <v>11890</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-6.22%</t>
+          <t>-4.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="E16" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>17.58</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,58 +1883,334 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14710</v>
+        <v>12450</v>
       </c>
       <c r="K16" t="n">
-        <v>14710</v>
+        <v>11960</v>
       </c>
       <c r="L16" t="n">
-        <v>15420</v>
+        <v>13900</v>
       </c>
       <c r="M16" t="n">
-        <v>13700</v>
+        <v>11810</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>17.07</v>
       </c>
       <c r="O16" t="n">
-        <v>23184791865</v>
+        <v>51731379125</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>14350</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>465</v>
       </c>
       <c r="R16" t="n">
-        <v>-63000</v>
+        <v>69000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>수주 소식에도 불구하고 주가 하락 및 투자 심리 위축. 재건축 사업 시공사 선정 등 긍정적 뉴스에도 부정적 전망.</t>
+          <t>외국인 대량 매수세 유입되며 급등 기대감 형성. 단기 급등 후 주가 조정 및 변동성 확대, 수급 변화 주목.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['외국인 매수', '급등 기대', '주가 변동성']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>18890</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-5.03%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" t="n">
+        <v>31</v>
+      </c>
+      <c r="G17" t="n">
+        <v>239</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>19890</v>
+      </c>
+      <c r="K17" t="n">
+        <v>19480</v>
+      </c>
+      <c r="L17" t="n">
+        <v>19550</v>
+      </c>
+      <c r="M17" t="n">
+        <v>18780</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>42958911610</v>
+      </c>
+      <c r="P17" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>대차 해지 운동 및 공매도 세력과의 대립 구도 형성. 저점 매수 기회 및 주가 반등 기대감 언급, 투자자 참여 독려.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
         <v>0.2</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>['수주', '재건축', '하락']</t>
-        </is>
-      </c>
-      <c r="X16" t="n">
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['대차 해지', '공매도', '반등 기대']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1716000</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-5.30%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>800</v>
+      </c>
+      <c r="F18" t="n">
+        <v>530</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1241</v>
+      </c>
+      <c r="H18" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1812000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1707000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1729000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1695000</v>
+      </c>
+      <c r="N18" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3061586835000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>325000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-662000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-142000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>반도체 업황 부진 및 공매도 압박 속에 주가 하락세 지속. 시장 전반의 하락세 및 부정적 전망, 현금 보유 전략 권고.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['반도체 업황', '공매도', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>13870</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-5.71%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>63</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40</v>
+      </c>
+      <c r="G19" t="n">
+        <v>163</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>14710</v>
+      </c>
+      <c r="K19" t="n">
+        <v>14710</v>
+      </c>
+      <c r="L19" t="n">
+        <v>15420</v>
+      </c>
+      <c r="M19" t="n">
+        <v>13700</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>23492949845</v>
+      </c>
+      <c r="P19" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-63000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>수원 파장1구역 재건축 시공사 선정 소식에도 불구하고, 부동산 시장 침체 및 외인 매도세로 주가 하락. 1만원대 지지선 약화 우려.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['재건축', '부동산 침체', '외인 매도']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
         <v>53</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>002990</t>
         </is>
